--- a/data/trans_camb/P6907S1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 15,41</t>
+          <t>-7,73; 13,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 8,66</t>
+          <t>-7,36; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 9,34</t>
+          <t>-7,79; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -2,34</t>
+          <t>-20,83; -2,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,19; -2,33</t>
+          <t>-20,81; -2,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 3,86</t>
+          <t>-17,51; 5,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 5,17</t>
+          <t>-9,33; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 5,04</t>
+          <t>-8,26; 5,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 4,49</t>
+          <t>-7,72; 4,67</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 425,12</t>
+          <t>-100,0; 477,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 318,99</t>
+          <t>-100,0; 268,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 262,47</t>
+          <t>-100,0; 337,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,95</t>
+          <t>-100,0; 160,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,16</t>
+          <t>-100,0; 146,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,36; 119,84</t>
+          <t>-87,45; 119,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,26</t>
+          <t>-8,86; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -2,0</t>
+          <t>-10,65; -2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,56</t>
+          <t>-5,14; 5,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -4,22</t>
+          <t>-14,21; -4,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -2,38</t>
+          <t>-12,72; -1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,8</t>
+          <t>-7,76; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,71</t>
+          <t>-9,59; -0,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -3,26</t>
+          <t>-10,5; -3,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,06</t>
+          <t>-5,09; 2,86</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 70,96</t>
+          <t>-77,36; 55,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,87; -22,67</t>
+          <t>-88,38; -26,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 87,64</t>
+          <t>-45,06; 79,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,84</t>
+          <t>-100,0; -12,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 77,76</t>
+          <t>-60,14; 102,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,18; -3,96</t>
+          <t>-86,2; -3,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,7; -43,29</t>
+          <t>-88,11; -43,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 45,22</t>
+          <t>-44,98; 42,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,41; -6,6</t>
+          <t>-22,94; -5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -1,98</t>
+          <t>-20,81; -1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 19,86</t>
+          <t>-7,07; 20,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 31,48</t>
+          <t>-15,75; 30,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,3; -2,61</t>
+          <t>-22,79; -1,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 8,94</t>
+          <t>-15,74; 8,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 7,48</t>
+          <t>-16,25; 8,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -3,75</t>
+          <t>-18,92; -4,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 10,03</t>
+          <t>-8,06; 9,37</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,87</t>
+          <t>-100,0; 16,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 244,84</t>
+          <t>-46,08; 301,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 341,09</t>
+          <t>-100,0; 283,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,09; -0,29</t>
+          <t>-95,67; -0,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 102,34</t>
+          <t>-64,37; 92,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,86</t>
+          <t>-100,0; 100,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,33; -27,04</t>
+          <t>-92,2; -28,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 100,98</t>
+          <t>-44,49; 88,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,05</t>
+          <t>-8,15; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -2,32</t>
+          <t>-9,11; -2,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 7,03</t>
+          <t>-2,5; 6,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -2,21</t>
+          <t>-13,33; -2,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -3,75</t>
+          <t>-13,36; -4,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 2,5</t>
+          <t>-8,18; 1,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,63</t>
+          <t>-8,81; -1,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -3,92</t>
+          <t>-9,2; -3,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,03</t>
+          <t>-3,58; 3,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 20,46</t>
+          <t>-75,87; 17,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,88; -27,86</t>
+          <t>-79,99; -29,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 100,6</t>
+          <t>-24,22; 91,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-92,52; -9,92</t>
+          <t>-100,0; -19,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-93,29; -43,66</t>
+          <t>-93,2; -45,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 32,72</t>
+          <t>-56,98; 18,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -15,37</t>
+          <t>-77,5; -14,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,99; -47,27</t>
+          <t>-81,44; -45,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 37,12</t>
+          <t>-32,87; 38,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6907S1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,86</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-2,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 13,24</t>
+          <t>-7,54; 12,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 8,77</t>
+          <t>-7,13; 9,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 10,67</t>
+          <t>-8,66; 7,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -2,23</t>
+          <t>-21,65; -2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -2,22</t>
+          <t>-20,98; -2,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 5,09</t>
+          <t>-14,2; 8,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,08</t>
+          <t>-8,81; 4,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 5,27</t>
+          <t>-8,48; 4,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 4,67</t>
+          <t>-7,91; 4,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,27%</t>
+          <t>-34,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-60,62%</t>
+          <t>-30,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,82%</t>
+          <t>-30,85%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 477,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,86</t>
+          <t>-80,57; 302,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 337,26</t>
+          <t>-100,0; 234,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,94</t>
+          <t>-100,0; 130,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,84</t>
+          <t>-87,95; 126,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,45; 119,03</t>
+          <t>-85,19; 99,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,42</t>
+          <t>-8,54; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -2,09</t>
+          <t>-10,59; -1,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 5,15</t>
+          <t>-5,04; 5,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -4,18</t>
+          <t>-14,45; -4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,91</t>
+          <t>-13,15; -2,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 4,43</t>
+          <t>-6,87; 5,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -0,72</t>
+          <t>-8,98; -1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -3,43</t>
+          <t>-9,72; -2,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,86</t>
+          <t>-4,59; 3,22</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>-0,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-19,32%</t>
+          <t>-5,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,7%</t>
+          <t>-4,09%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,36; 55,49</t>
+          <t>-76,52; 71,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,38; -26,94</t>
+          <t>-86,62; -15,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 79,53</t>
+          <t>-43,25; 83,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,68</t>
+          <t>-100,0; -4,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 102,87</t>
+          <t>-53,4; 126,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,2; -3,54</t>
+          <t>-84,04; -6,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,11; -43,99</t>
+          <t>-87,02; -39,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 42,07</t>
+          <t>-39,27; 49,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -5,4</t>
+          <t>-22,83; -6,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -1,99</t>
+          <t>-20,73; -2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 20,32</t>
+          <t>-7,7; 17,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 30,61</t>
+          <t>-15,24; 29,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -1,64</t>
+          <t>-23,28; -2,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 8,04</t>
+          <t>-16,91; 7,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 8,91</t>
+          <t>-15,18; 7,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,92; -4,07</t>
+          <t>-18,71; -4,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 9,37</t>
+          <t>-9,07; 8,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-21,47%</t>
+          <t>-21,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,24</t>
+          <t>-100,0; 6,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 301,18</t>
+          <t>-47,91; 246,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,98</t>
+          <t>-75,03; 257,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-95,67; -0,46</t>
+          <t>-100,0; 2,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,37; 92,87</t>
+          <t>-66,51; 89,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,77</t>
+          <t>-84,48; 81,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-92,2; -28,41</t>
+          <t>-91,57; -26,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 88,9</t>
+          <t>-48,3; 89,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,01</t>
+          <t>-8,19; 1,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -2,48</t>
+          <t>-8,88; -2,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,87</t>
+          <t>-3,12; 6,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,67</t>
+          <t>-12,88; -2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,09</t>
+          <t>-13,14; -3,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,52</t>
+          <t>-7,15; 3,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,36</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -3,83</t>
+          <t>-9,75; -4,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,01</t>
+          <t>-3,15; 3,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,11%</t>
+          <t>-13,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,26%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 17,28</t>
+          <t>-74,98; 30,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,99; -29,01</t>
+          <t>-80,75; -27,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 91,74</t>
+          <t>-29,59; 83,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,6</t>
+          <t>-93,37; -20,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -45,35</t>
+          <t>-92,99; -43,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 18,15</t>
+          <t>-48,89; 45,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -14,71</t>
+          <t>-76,33; -17,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,44; -45,27</t>
+          <t>-82,02; -46,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 38,52</t>
+          <t>-28,49; 35,53</t>
         </is>
       </c>
     </row>
